--- a/checklists/excel/self/tests.xlsx
+++ b/checklists/excel/self/tests.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Test Review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,94 +425,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item Text</t>
+          <t>Sr.No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Main Category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Sub Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to Measure</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Unit tests cover critical business logic (MUST)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Test Review</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Core algorithms tested; Edge cases covered; Test data realistic</t>
+          <t>Verify unit tests cover critical business logic</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ensure core algorithms are tested, edge cases are covered, and test data is realistic for essential business logic.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Essential business logic must have comprehensive unit test coverage</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Test coverage analysis and code review</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Integration tests verify component interactions (GOOD)</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Test Review</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>API endpoints tested; Database interactions verified; External service mocks</t>
+          <t>Check integration tests verify component interactions</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ensure API endpoints are tested, database interactions are verified, and external service mocks are properly implemented.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Integration tests ensure components work together correctly</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Run integration test suite and review test results</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Test coverage meets project requirements (GOOD)</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Test Review</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minimum coverage threshold met; Critical paths covered; Coverage reports reviewed</t>
+          <t>Verify test coverage meets project requirements</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ensure minimum coverage threshold is met, critical paths are covered, and coverage reports are reviewed.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Test coverage should meet or exceed project standards</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Generate and review coverage reports</t>
         </is>
       </c>
     </row>
